--- a/data/mappings/mapping_agences_code_ria.xlsx
+++ b/data/mappings/mapping_agences_code_ria.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ndick.faye\Documents\PROJET RECONCILIATION  OPS\RECON\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\haby.sow\Downloads\reconciliation-git\data\mappings\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF7C1E93-97C5-46E7-903F-40F6D3FC7509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8300"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MAPPING_AGENCES" sheetId="1" r:id="rId1"/>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
   <si>
     <t>CODE_AGENCE</t>
   </si>
@@ -268,12 +269,21 @@
   </si>
   <si>
     <t>COFINA ZIGUINCHOR</t>
+  </si>
+  <si>
+    <t>AGENCE KEUR MASSAR</t>
+  </si>
+  <si>
+    <t>COFINA KEUR MASSAR</t>
+  </si>
+  <si>
+    <t>COFI030</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -356,7 +366,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -658,8 +668,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D27"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="31.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="57.7265625" customWidth="1"/>
@@ -1044,8 +1054,22 @@
         <v>81</v>
       </c>
     </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" s="2">
+        <v>527</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D27"/>
+  <autoFilter ref="A1:D27" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>